--- a/artfynd/A 48151-2019 artfynd.xlsx
+++ b/artfynd/A 48151-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48151-2019 artfynd.xlsx
+++ b/artfynd/A 48151-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY179"/>
+  <dimension ref="A1:AY178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13147,10 +13147,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>91962531</v>
+        <v>91961413</v>
       </c>
       <c r="B113" t="n">
-        <v>78503</v>
+        <v>81236</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13159,25 +13159,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>648838.1493882204</v>
+        <v>648905.8056089107</v>
       </c>
       <c r="R113" t="n">
-        <v>7018579.881156802</v>
+        <v>7018483.818156593</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13259,10 +13259,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>91961413</v>
+        <v>91960597</v>
       </c>
       <c r="B114" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13275,21 +13275,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>648905.8056089107</v>
+        <v>649064.9029093307</v>
       </c>
       <c r="R114" t="n">
-        <v>7018483.818156593</v>
+        <v>7018373.051542088</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>91960597</v>
+        <v>91961496</v>
       </c>
       <c r="B115" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13387,21 +13387,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>649064.9029093307</v>
+        <v>648950.185312101</v>
       </c>
       <c r="R115" t="n">
-        <v>7018373.051542088</v>
+        <v>7018432.216481163</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -13483,10 +13483,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>91961496</v>
+        <v>91960606</v>
       </c>
       <c r="B116" t="n">
-        <v>77506</v>
+        <v>89392</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13499,21 +13499,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13523,10 +13523,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>648950.185312101</v>
+        <v>648841.1133945474</v>
       </c>
       <c r="R116" t="n">
-        <v>7018432.216481163</v>
+        <v>7018506.07364818</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -13595,7 +13595,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>91960606</v>
+        <v>91960612</v>
       </c>
       <c r="B117" t="n">
         <v>89392</v>
@@ -13635,10 +13635,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>648841.1133945474</v>
+        <v>648830.1164190442</v>
       </c>
       <c r="R117" t="n">
-        <v>7018506.07364818</v>
+        <v>7018694.931869064</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -13707,7 +13707,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>91960612</v>
+        <v>91960601</v>
       </c>
       <c r="B118" t="n">
         <v>89392</v>
@@ -13747,10 +13747,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>648830.1164190442</v>
+        <v>649022.8902813313</v>
       </c>
       <c r="R118" t="n">
-        <v>7018694.931869064</v>
+        <v>7018431.976940131</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -13819,10 +13819,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>91960601</v>
+        <v>91960368</v>
       </c>
       <c r="B119" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13831,25 +13831,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13859,10 +13859,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>649022.8902813313</v>
+        <v>649067.105801584</v>
       </c>
       <c r="R119" t="n">
-        <v>7018431.976940131</v>
+        <v>7018383.975430635</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13931,10 +13931,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>91960368</v>
+        <v>91961113</v>
       </c>
       <c r="B120" t="n">
-        <v>89356</v>
+        <v>78569</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13943,25 +13943,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13971,10 +13971,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>649067.105801584</v>
+        <v>649060.9374449125</v>
       </c>
       <c r="R120" t="n">
-        <v>7018383.975430635</v>
+        <v>7018487.847535552</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14043,10 +14043,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>91961113</v>
+        <v>91961423</v>
       </c>
       <c r="B121" t="n">
-        <v>78569</v>
+        <v>81236</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14059,21 +14059,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>649060.9374449125</v>
+        <v>648845.885891977</v>
       </c>
       <c r="R121" t="n">
-        <v>7018487.847535552</v>
+        <v>7018559.047890401</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -14155,7 +14155,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>91961423</v>
+        <v>91961419</v>
       </c>
       <c r="B122" t="n">
         <v>81236</v>
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>648845.885891977</v>
+        <v>648835.9048406942</v>
       </c>
       <c r="R122" t="n">
-        <v>7018559.047890401</v>
+        <v>7018677.165250384</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -14267,10 +14267,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>91961419</v>
+        <v>91962538</v>
       </c>
       <c r="B123" t="n">
-        <v>81236</v>
+        <v>78503</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14279,25 +14279,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14307,10 +14307,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>648835.9048406942</v>
+        <v>649244.0296848449</v>
       </c>
       <c r="R123" t="n">
-        <v>7018677.165250384</v>
+        <v>7018229.848300115</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -14379,10 +14379,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>91962538</v>
+        <v>91961495</v>
       </c>
       <c r="B124" t="n">
-        <v>78503</v>
+        <v>77506</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14391,25 +14391,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14419,10 +14419,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>649244.0296848449</v>
+        <v>649150.8890418999</v>
       </c>
       <c r="R124" t="n">
-        <v>7018229.848300115</v>
+        <v>7018290.912622792</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -14491,10 +14491,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>91961495</v>
+        <v>91960604</v>
       </c>
       <c r="B125" t="n">
-        <v>77506</v>
+        <v>89392</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14507,21 +14507,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>649150.8890418999</v>
+        <v>648998.0059168604</v>
       </c>
       <c r="R125" t="n">
-        <v>7018290.912622792</v>
+        <v>7018433.078624073</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -14603,10 +14603,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>91960604</v>
+        <v>91961427</v>
       </c>
       <c r="B126" t="n">
-        <v>89392</v>
+        <v>81236</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14619,21 +14619,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14643,10 +14643,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>648998.0059168604</v>
+        <v>648840.9792235605</v>
       </c>
       <c r="R126" t="n">
-        <v>7018433.078624073</v>
+        <v>7018547.999686122</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14715,7 +14715,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>91961427</v>
+        <v>91961407</v>
       </c>
       <c r="B127" t="n">
         <v>81236</v>
@@ -14755,10 +14755,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>648840.9792235605</v>
+        <v>649105.1647877604</v>
       </c>
       <c r="R127" t="n">
-        <v>7018547.999686122</v>
+        <v>7018303.222257292</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14827,10 +14827,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>91961407</v>
+        <v>91962535</v>
       </c>
       <c r="B128" t="n">
-        <v>81236</v>
+        <v>78503</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14839,25 +14839,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14867,10 +14867,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>649105.1647877604</v>
+        <v>649329.149675598</v>
       </c>
       <c r="R128" t="n">
-        <v>7018303.222257292</v>
+        <v>7018322.180165272</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -14939,7 +14939,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>91962535</v>
+        <v>91962537</v>
       </c>
       <c r="B129" t="n">
         <v>78503</v>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>649329.149675598</v>
+        <v>649268.2201239206</v>
       </c>
       <c r="R129" t="n">
-        <v>7018322.180165272</v>
+        <v>7018204.816578459</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -15051,10 +15051,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>91962537</v>
+        <v>95560762</v>
       </c>
       <c r="B130" t="n">
-        <v>78503</v>
+        <v>89356</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15067,37 +15067,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Osbodarna, Ång</t>
+          <t>Stor-Hustjärnen, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>649268.2201239206</v>
+        <v>649048.2160597442</v>
       </c>
       <c r="R130" t="n">
-        <v>7018204.816578459</v>
+        <v>7018392.118202308</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2020-06-08</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
@@ -15151,22 +15151,26 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Kristin Lindström</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>95560762</v>
+        <v>95560765</v>
       </c>
       <c r="B131" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15175,25 +15179,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15203,10 +15207,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>649048.2160597442</v>
+        <v>649385.4648802081</v>
       </c>
       <c r="R131" t="n">
-        <v>7018392.118202308</v>
+        <v>7018130.442497737</v>
       </c>
       <c r="S131" t="n">
         <v>20</v>
@@ -15279,10 +15283,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>95560765</v>
+        <v>95560761</v>
       </c>
       <c r="B132" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15291,25 +15295,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15319,10 +15323,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>649385.4648802081</v>
+        <v>649432.2102433246</v>
       </c>
       <c r="R132" t="n">
-        <v>7018130.442497737</v>
+        <v>7018387.840041455</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>
@@ -15395,10 +15399,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>95560761</v>
+        <v>95560767</v>
       </c>
       <c r="B133" t="n">
-        <v>89356</v>
+        <v>96334</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15407,25 +15411,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15435,10 +15439,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>649432.2102433246</v>
+        <v>649368.4285663011</v>
       </c>
       <c r="R133" t="n">
-        <v>7018387.840041455</v>
+        <v>7018370.899260637</v>
       </c>
       <c r="S133" t="n">
         <v>20</v>
@@ -15511,10 +15515,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>95560767</v>
+        <v>95560763</v>
       </c>
       <c r="B134" t="n">
-        <v>96334</v>
+        <v>89392</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15523,25 +15527,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15551,10 +15555,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>649368.4285663011</v>
+        <v>649253.7509728664</v>
       </c>
       <c r="R134" t="n">
-        <v>7018370.899260637</v>
+        <v>7018516.628305382</v>
       </c>
       <c r="S134" t="n">
         <v>20</v>
@@ -15627,7 +15631,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>95560763</v>
+        <v>95560766</v>
       </c>
       <c r="B135" t="n">
         <v>89392</v>
@@ -15667,10 +15671,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>649253.7509728664</v>
+        <v>649039.2466794063</v>
       </c>
       <c r="R135" t="n">
-        <v>7018516.628305382</v>
+        <v>7018390.800780035</v>
       </c>
       <c r="S135" t="n">
         <v>20</v>
@@ -15743,10 +15747,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>95560766</v>
+        <v>100364283</v>
       </c>
       <c r="B136" t="n">
-        <v>89392</v>
+        <v>56540</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15759,37 +15763,49 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stor-Hustjärnen, Ång</t>
+          <t>Stor-Hustjärn, Hannsjön, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>649039.2466794063</v>
+        <v>648858.5120595266</v>
       </c>
       <c r="R136" t="n">
-        <v>7018390.800780035</v>
+        <v>7018598.407686125</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15813,7 +15829,7 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
@@ -15823,7 +15839,7 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
@@ -15843,26 +15859,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>100364283</v>
+        <v>100364274</v>
       </c>
       <c r="B137" t="n">
-        <v>56540</v>
+        <v>89356</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15871,50 +15883,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Stor-Hustjärn, Hannsjön, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>648858.5120595266</v>
+        <v>649044.6879747212</v>
       </c>
       <c r="R137" t="n">
-        <v>7018598.407686125</v>
+        <v>7018448.768394668</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15941,7 +15941,7 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
@@ -15983,10 +15983,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>100364274</v>
+        <v>100364272</v>
       </c>
       <c r="B138" t="n">
-        <v>89356</v>
+        <v>73693</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15995,25 +15995,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16023,10 +16023,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>649044.6879747212</v>
+        <v>648910.0556663114</v>
       </c>
       <c r="R138" t="n">
-        <v>7018448.768394668</v>
+        <v>7018470.037254798</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -16053,7 +16053,7 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
@@ -16095,10 +16095,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>100364272</v>
+        <v>100364287</v>
       </c>
       <c r="B139" t="n">
-        <v>73693</v>
+        <v>89403</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16107,25 +16107,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6440</v>
+        <v>1205</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>648910.0556663114</v>
+        <v>648848.61924244</v>
       </c>
       <c r="R139" t="n">
-        <v>7018470.037254798</v>
+        <v>7018519.496701576</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16207,10 +16207,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>100364287</v>
+        <v>100364296</v>
       </c>
       <c r="B140" t="n">
-        <v>89403</v>
+        <v>93044</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16223,21 +16223,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1205</v>
+        <v>2809</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16247,10 +16247,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>648848.61924244</v>
+        <v>649442.9126851113</v>
       </c>
       <c r="R140" t="n">
-        <v>7018519.496701576</v>
+        <v>7018244.943934884</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16277,7 +16277,7 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
@@ -16319,10 +16319,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>100364296</v>
+        <v>100364285</v>
       </c>
       <c r="B141" t="n">
-        <v>93044</v>
+        <v>89403</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16335,21 +16335,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2809</v>
+        <v>1205</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16359,10 +16359,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>649442.9126851113</v>
+        <v>649449.334598915</v>
       </c>
       <c r="R141" t="n">
-        <v>7018244.943934884</v>
+        <v>7018233.067091271</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -16431,10 +16431,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>100364285</v>
+        <v>100364282</v>
       </c>
       <c r="B142" t="n">
-        <v>89403</v>
+        <v>89392</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16443,25 +16443,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16471,10 +16471,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>649449.334598915</v>
+        <v>648883.287533096</v>
       </c>
       <c r="R142" t="n">
-        <v>7018233.067091271</v>
+        <v>7018550.859602048</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
@@ -16543,10 +16543,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>100364282</v>
+        <v>100364322</v>
       </c>
       <c r="B143" t="n">
-        <v>89392</v>
+        <v>81236</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16559,21 +16559,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16583,10 +16583,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>648883.287533096</v>
+        <v>648880.0296838729</v>
       </c>
       <c r="R143" t="n">
-        <v>7018550.859602048</v>
+        <v>7018552.963206837</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -16637,6 +16637,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -16655,10 +16656,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>100364322</v>
+        <v>100364281</v>
       </c>
       <c r="B144" t="n">
-        <v>81236</v>
+        <v>89392</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16671,21 +16672,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16695,10 +16696,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>648880.0296838729</v>
+        <v>648945.471353092</v>
       </c>
       <c r="R144" t="n">
-        <v>7018552.963206837</v>
+        <v>7018514.511677563</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16749,7 +16750,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -16768,10 +16768,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>100364281</v>
+        <v>100364273</v>
       </c>
       <c r="B145" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16780,25 +16780,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16808,10 +16808,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>648945.471353092</v>
+        <v>649451.3250545261</v>
       </c>
       <c r="R145" t="n">
-        <v>7018514.511677563</v>
+        <v>7018229.101157954</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
@@ -16880,10 +16880,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>100364273</v>
+        <v>100364280</v>
       </c>
       <c r="B146" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16892,25 +16892,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16920,10 +16920,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>649451.3250545261</v>
+        <v>648845.9727289622</v>
       </c>
       <c r="R146" t="n">
-        <v>7018229.101157954</v>
+        <v>7018498.633426901</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
@@ -16992,7 +16992,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>100364280</v>
+        <v>100364276</v>
       </c>
       <c r="B147" t="n">
         <v>89392</v>
@@ -17032,10 +17032,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>648845.9727289622</v>
+        <v>649276.6229035142</v>
       </c>
       <c r="R147" t="n">
-        <v>7018498.633426901</v>
+        <v>7018198.893399956</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -17062,7 +17062,7 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
@@ -17104,10 +17104,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>100364276</v>
+        <v>100364319</v>
       </c>
       <c r="B148" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -17120,21 +17120,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17144,10 +17144,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>649276.6229035142</v>
+        <v>648848.61924244</v>
       </c>
       <c r="R148" t="n">
-        <v>7018198.893399956</v>
+        <v>7018519.496701576</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
@@ -17216,10 +17216,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>100364319</v>
+        <v>100364303</v>
       </c>
       <c r="B149" t="n">
-        <v>77506</v>
+        <v>78527</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17228,25 +17228,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17256,10 +17256,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>648848.61924244</v>
+        <v>649451.6039369672</v>
       </c>
       <c r="R149" t="n">
-        <v>7018519.496701576</v>
+        <v>7018193.941015964</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -17286,7 +17286,7 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
@@ -17296,7 +17296,7 @@
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
@@ -17328,10 +17328,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>100364303</v>
+        <v>100364320</v>
       </c>
       <c r="B150" t="n">
-        <v>78527</v>
+        <v>77506</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -17340,25 +17340,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17368,10 +17368,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>649451.6039369672</v>
+        <v>648858.5120595266</v>
       </c>
       <c r="R150" t="n">
-        <v>7018193.941015964</v>
+        <v>7018598.407686125</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
@@ -17440,10 +17440,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>100364320</v>
+        <v>100364304</v>
       </c>
       <c r="B151" t="n">
-        <v>77506</v>
+        <v>78527</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17452,25 +17452,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17480,10 +17480,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>648858.5120595266</v>
+        <v>649449.334598915</v>
       </c>
       <c r="R151" t="n">
-        <v>7018598.407686125</v>
+        <v>7018233.067091271</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
@@ -17552,10 +17552,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>100364304</v>
+        <v>100364317</v>
       </c>
       <c r="B152" t="n">
-        <v>78527</v>
+        <v>77506</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17564,25 +17564,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17592,10 +17592,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>649449.334598915</v>
+        <v>649059.4987152913</v>
       </c>
       <c r="R152" t="n">
-        <v>7018233.067091271</v>
+        <v>7018518.89232898</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17664,10 +17664,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>100364317</v>
+        <v>100364310</v>
       </c>
       <c r="B153" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -17680,21 +17680,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17704,10 +17704,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>649059.4987152913</v>
+        <v>648978.7435622349</v>
       </c>
       <c r="R153" t="n">
-        <v>7018518.89232898</v>
+        <v>7018498.017059882</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
@@ -17744,7 +17744,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
@@ -17776,10 +17776,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>100364310</v>
+        <v>100364292</v>
       </c>
       <c r="B154" t="n">
-        <v>89410</v>
+        <v>89832</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17788,25 +17788,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17816,10 +17816,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>648978.7435622349</v>
+        <v>649206.3566702341</v>
       </c>
       <c r="R154" t="n">
-        <v>7018498.017059882</v>
+        <v>7018380.060929063</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
@@ -17888,10 +17888,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>100364292</v>
+        <v>100364311</v>
       </c>
       <c r="B155" t="n">
-        <v>89832</v>
+        <v>77506</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17900,25 +17900,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17928,10 +17928,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>649206.3566702341</v>
+        <v>648978.7435622349</v>
       </c>
       <c r="R155" t="n">
-        <v>7018380.060929063</v>
+        <v>7018498.017059882</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -18000,10 +18000,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>100364311</v>
+        <v>100364297</v>
       </c>
       <c r="B156" t="n">
-        <v>77506</v>
+        <v>78569</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -18016,34 +18016,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Stor-Hustjärn, Hannsjön, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>648978.7435622349</v>
+        <v>649050.5170025714</v>
       </c>
       <c r="R156" t="n">
-        <v>7018498.017059882</v>
+        <v>7018508.105640701</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -18088,12 +18091,18 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På flera träd</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -18112,10 +18121,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>100364297</v>
+        <v>100364301</v>
       </c>
       <c r="B157" t="n">
-        <v>78569</v>
+        <v>78603</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -18124,41 +18133,38 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Stor-Hustjärn, Hannsjön, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>649050.5170025714</v>
+        <v>649267.6860247531</v>
       </c>
       <c r="R157" t="n">
-        <v>7018508.105640701</v>
+        <v>7018206.595535902</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -18203,18 +18209,12 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På flera träd</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
@@ -18233,10 +18233,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>100364301</v>
+        <v>100364278</v>
       </c>
       <c r="B158" t="n">
-        <v>78603</v>
+        <v>89392</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -18245,25 +18245,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -18273,10 +18273,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>649267.6860247531</v>
+        <v>649181.6671409321</v>
       </c>
       <c r="R158" t="n">
-        <v>7018206.595535902</v>
+        <v>7018415.89015879</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>100364278</v>
+        <v>100364299</v>
       </c>
       <c r="B159" t="n">
-        <v>89392</v>
+        <v>78569</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -18361,21 +18361,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>649181.6671409321</v>
+        <v>648848.61924244</v>
       </c>
       <c r="R159" t="n">
-        <v>7018415.89015879</v>
+        <v>7018519.496701576</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -18415,7 +18415,7 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
@@ -18425,7 +18425,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
@@ -18457,7 +18457,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>100364299</v>
+        <v>100364298</v>
       </c>
       <c r="B160" t="n">
         <v>78569</v>
@@ -18497,10 +18497,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>648848.61924244</v>
+        <v>648885.3604059115</v>
       </c>
       <c r="R160" t="n">
-        <v>7018519.496701576</v>
+        <v>7018545.094087722</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18569,10 +18569,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>100364298</v>
+        <v>100364284</v>
       </c>
       <c r="B161" t="n">
-        <v>78569</v>
+        <v>78596</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18581,38 +18581,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Stor-Hustjärn, Hannsjön, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>648885.3604059115</v>
+        <v>649119.8249006653</v>
       </c>
       <c r="R161" t="n">
-        <v>7018545.094087722</v>
+        <v>7018357.109907075</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18639,7 +18642,7 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
@@ -18649,7 +18652,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
@@ -18657,12 +18660,18 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18681,10 +18690,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>100364284</v>
+        <v>100364302</v>
       </c>
       <c r="B162" t="n">
-        <v>78596</v>
+        <v>78527</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18697,21 +18706,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18802,10 +18811,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>100364302</v>
+        <v>100364293</v>
       </c>
       <c r="B163" t="n">
-        <v>78527</v>
+        <v>89673</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18814,41 +18823,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229497</v>
+        <v>658</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Stor-Hustjärn, Hannsjön, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>649119.8249006653</v>
+        <v>648945.471353092</v>
       </c>
       <c r="R163" t="n">
-        <v>7018357.109907075</v>
+        <v>7018514.511677563</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18875,7 +18881,7 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr">
@@ -18885,7 +18891,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
@@ -18893,18 +18899,12 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD163" t="b">
         <v>0</v>
       </c>
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -18923,10 +18923,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>100364293</v>
+        <v>100364277</v>
       </c>
       <c r="B164" t="n">
-        <v>89673</v>
+        <v>89392</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18939,21 +18939,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>648945.471353092</v>
+        <v>649206.3566702341</v>
       </c>
       <c r="R164" t="n">
-        <v>7018514.511677563</v>
+        <v>7018380.060929063</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18993,7 +18993,7 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
@@ -19035,10 +19035,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>100364277</v>
+        <v>100364318</v>
       </c>
       <c r="B165" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19051,21 +19051,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -19075,10 +19075,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>649206.3566702341</v>
+        <v>649013.535979457</v>
       </c>
       <c r="R165" t="n">
-        <v>7018380.060929063</v>
+        <v>7018526.682101555</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -19147,7 +19147,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>100364318</v>
+        <v>100364312</v>
       </c>
       <c r="B166" t="n">
         <v>77506</v>
@@ -19187,10 +19187,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>649013.535979457</v>
+        <v>649185.0439993965</v>
       </c>
       <c r="R166" t="n">
-        <v>7018526.682101555</v>
+        <v>7018323.609971339</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -19259,7 +19259,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>100364312</v>
+        <v>100364313</v>
       </c>
       <c r="B167" t="n">
         <v>77506</v>
@@ -19299,10 +19299,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>649185.0439993965</v>
+        <v>648866.9682127519</v>
       </c>
       <c r="R167" t="n">
-        <v>7018323.609971339</v>
+        <v>7018493.743546856</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
@@ -19371,10 +19371,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>100364313</v>
+        <v>100364290</v>
       </c>
       <c r="B168" t="n">
-        <v>77506</v>
+        <v>78503</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -19383,25 +19383,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -19411,10 +19411,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>648866.9682127519</v>
+        <v>649267.6860247531</v>
       </c>
       <c r="R168" t="n">
-        <v>7018493.743546856</v>
+        <v>7018206.595535902</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
@@ -19483,10 +19483,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>100364290</v>
+        <v>100364308</v>
       </c>
       <c r="B169" t="n">
-        <v>78503</v>
+        <v>78479</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19495,25 +19495,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19523,10 +19523,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>649267.6860247531</v>
+        <v>649320.8724235061</v>
       </c>
       <c r="R169" t="n">
-        <v>7018206.595535902</v>
+        <v>7018325.403270377</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -19595,10 +19595,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>100364308</v>
+        <v>100364316</v>
       </c>
       <c r="B170" t="n">
-        <v>78479</v>
+        <v>77506</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19607,25 +19607,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19635,10 +19635,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>649320.8724235061</v>
+        <v>649403.6315503619</v>
       </c>
       <c r="R170" t="n">
-        <v>7018325.403270377</v>
+        <v>7018264.312993236</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -19707,10 +19707,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>100364316</v>
+        <v>100364309</v>
       </c>
       <c r="B171" t="n">
-        <v>77506</v>
+        <v>78479</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19719,25 +19719,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>392</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19747,10 +19747,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>649403.6315503619</v>
+        <v>649399.6508029685</v>
       </c>
       <c r="R171" t="n">
-        <v>7018264.312993236</v>
+        <v>7018272.244819109</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -19819,10 +19819,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>100364309</v>
+        <v>100364275</v>
       </c>
       <c r="B172" t="n">
-        <v>78479</v>
+        <v>89392</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19831,25 +19831,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>649399.6508029685</v>
+        <v>649231.6120057573</v>
       </c>
       <c r="R172" t="n">
-        <v>7018272.244819109</v>
+        <v>7018283.383521797</v>
       </c>
       <c r="S172" t="n">
         <v>15</v>
@@ -19931,10 +19931,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>100364275</v>
+        <v>100364305</v>
       </c>
       <c r="B173" t="n">
-        <v>89392</v>
+        <v>78527</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19943,25 +19943,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>649231.6120057573</v>
+        <v>649059.4987152913</v>
       </c>
       <c r="R173" t="n">
-        <v>7018283.383521797</v>
+        <v>7018518.89232898</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -20043,10 +20043,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>100364305</v>
+        <v>100364321</v>
       </c>
       <c r="B174" t="n">
-        <v>78527</v>
+        <v>81236</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -20055,25 +20055,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>649059.4987152913</v>
+        <v>649051.5504115195</v>
       </c>
       <c r="R174" t="n">
-        <v>7018518.89232898</v>
+        <v>7018446.831900408</v>
       </c>
       <c r="S174" t="n">
         <v>15</v>
@@ -20137,6 +20137,7 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -20155,10 +20156,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>100364321</v>
+        <v>100364289</v>
       </c>
       <c r="B175" t="n">
-        <v>81236</v>
+        <v>89403</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -20167,25 +20168,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1312</v>
+        <v>1205</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -20195,10 +20196,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>649051.5504115195</v>
+        <v>649403.6315503619</v>
       </c>
       <c r="R175" t="n">
-        <v>7018446.831900408</v>
+        <v>7018264.312993236</v>
       </c>
       <c r="S175" t="n">
         <v>15</v>
@@ -20249,7 +20250,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -20268,10 +20268,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>100364289</v>
+        <v>100364314</v>
       </c>
       <c r="B176" t="n">
-        <v>89403</v>
+        <v>77506</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20280,25 +20280,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -20308,10 +20308,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>649403.6315503619</v>
+        <v>648853.6395785663</v>
       </c>
       <c r="R176" t="n">
-        <v>7018264.312993236</v>
+        <v>7018596.378679123</v>
       </c>
       <c r="S176" t="n">
         <v>15</v>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr">
@@ -20380,10 +20380,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>100364314</v>
+        <v>100364271</v>
       </c>
       <c r="B177" t="n">
-        <v>77506</v>
+        <v>73693</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20396,21 +20396,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20420,10 +20420,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>648853.6395785663</v>
+        <v>648855.9829786473</v>
       </c>
       <c r="R177" t="n">
-        <v>7018596.378679123</v>
+        <v>7018477.453967626</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -20492,10 +20492,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>100364271</v>
+        <v>100364307</v>
       </c>
       <c r="B178" t="n">
-        <v>73693</v>
+        <v>89410</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20508,21 +20508,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20532,10 +20532,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>648855.9829786473</v>
+        <v>649063.5222131698</v>
       </c>
       <c r="R178" t="n">
-        <v>7018477.453967626</v>
+        <v>7018383.358448491</v>
       </c>
       <c r="S178" t="n">
         <v>15</v>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
@@ -20601,118 +20601,6 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>100364307</v>
-      </c>
-      <c r="B179" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>Stor-Hustjärn, Hannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q179" t="n">
-        <v>649063.5222131698</v>
-      </c>
-      <c r="R179" t="n">
-        <v>7018383.358448491</v>
-      </c>
-      <c r="S179" t="n">
-        <v>15</v>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>Örnsköldsvik</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>Sidensjö</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>2022-04-29</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT179" t="inlineStr"/>
-      <c r="AW179" t="inlineStr">
-        <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AX179" t="inlineStr">
-        <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
